--- a/research/traditional_assets/database/data/denmark/denmark_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09269999999999999</v>
+        <v>-0.00231</v>
       </c>
       <c r="E2">
-        <v>0.91</v>
+        <v>0.388</v>
       </c>
       <c r="G2">
-        <v>0.6818520172696144</v>
+        <v>0.3325013865779257</v>
       </c>
       <c r="H2">
-        <v>0.6818520172696144</v>
+        <v>0.3122573488630061</v>
       </c>
       <c r="I2">
-        <v>0.8262617239839213</v>
+        <v>0.310038824181919</v>
       </c>
       <c r="J2">
-        <v>0.7316171992366721</v>
+        <v>0.2762942670748261</v>
       </c>
       <c r="K2">
-        <v>2.180000000000001</v>
+        <v>9.219999999999999</v>
       </c>
       <c r="L2">
-        <v>0.1622748250707161</v>
+        <v>0.5113699389905711</v>
       </c>
       <c r="M2">
-        <v>3.99</v>
+        <v>6.651</v>
       </c>
       <c r="N2">
-        <v>0.02053525476067936</v>
+        <v>0.03676616915422885</v>
       </c>
       <c r="O2">
-        <v>1.830275229357798</v>
+        <v>0.7213665943600869</v>
       </c>
       <c r="P2">
-        <v>3.99</v>
+        <v>6.59</v>
       </c>
       <c r="Q2">
-        <v>0.02053525476067936</v>
+        <v>0.03642896627971254</v>
       </c>
       <c r="R2">
-        <v>1.830275229357798</v>
+        <v>0.7147505422993493</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.00917155314990227</v>
       </c>
       <c r="U2">
-        <v>7.85</v>
+        <v>3.7</v>
       </c>
       <c r="V2">
-        <v>0.04040144107050952</v>
+        <v>0.02045328911000553</v>
       </c>
       <c r="W2">
-        <v>-5.454841972606374</v>
+        <v>0.03198543345362267</v>
       </c>
       <c r="X2">
-        <v>0.02554270222960783</v>
+        <v>0.04988314538035492</v>
       </c>
       <c r="Y2">
-        <v>-5.480384674835982</v>
+        <v>-0.01789771192673224</v>
       </c>
       <c r="Z2">
-        <v>0.102651486207687</v>
+        <v>0.1281176721381369</v>
       </c>
       <c r="AA2">
-        <v>0.03283611246773181</v>
+        <v>0.01586436650481837</v>
       </c>
       <c r="AB2">
-        <v>0.02325753055856562</v>
+        <v>0.04894759380756151</v>
       </c>
       <c r="AC2">
-        <v>0.009578581909166183</v>
+        <v>-0.03308322730274314</v>
       </c>
       <c r="AD2">
-        <v>80.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>80.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="AG2">
-        <v>72.55000000000001</v>
+        <v>57</v>
       </c>
       <c r="AH2">
-        <v>0.2926829268292683</v>
+        <v>0.2512417218543046</v>
       </c>
       <c r="AI2">
-        <v>0.4721080446271286</v>
+        <v>0.3808030112923463</v>
       </c>
       <c r="AJ2">
-        <v>0.2718755855349447</v>
+        <v>0.2395964691046658</v>
       </c>
       <c r="AK2">
-        <v>0.4465989535241613</v>
+        <v>0.3660886319845857</v>
       </c>
       <c r="AL2">
-        <v>1.41</v>
+        <v>-3.55</v>
       </c>
       <c r="AM2">
-        <v>1.299</v>
+        <v>-6.01</v>
       </c>
       <c r="AN2">
-        <v>7.17857142857143</v>
+        <v>10.78152753108348</v>
       </c>
       <c r="AO2">
-        <v>7.872340425531915</v>
+        <v>-1.574647887323944</v>
       </c>
       <c r="AP2">
-        <v>6.477678571428573</v>
+        <v>10.12433392539964</v>
       </c>
       <c r="AQ2">
-        <v>8.545034642032332</v>
+        <v>-0.9301164725457571</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09269999999999999</v>
+        <v>-0.00231</v>
       </c>
       <c r="E3">
-        <v>0.91</v>
+        <v>0.388</v>
       </c>
       <c r="G3">
-        <v>0.663768115942029</v>
+        <v>0.701120797011208</v>
       </c>
       <c r="H3">
-        <v>0.663768115942029</v>
+        <v>0.701120797011208</v>
       </c>
       <c r="I3">
-        <v>0.8043478260869564</v>
+        <v>0.6961394769613948</v>
       </c>
       <c r="J3">
-        <v>0.6200790513833991</v>
+        <v>0.544604143302395</v>
       </c>
       <c r="K3">
-        <v>8.49</v>
+        <v>14.2</v>
       </c>
       <c r="L3">
-        <v>0.6152173913043478</v>
+        <v>1.768368617683686</v>
       </c>
       <c r="M3">
-        <v>3.99</v>
+        <v>6.59</v>
       </c>
       <c r="N3">
-        <v>0.04226694915254237</v>
+        <v>0.05213607594936708</v>
       </c>
       <c r="O3">
-        <v>0.4699646643109541</v>
+        <v>0.4640845070422535</v>
       </c>
       <c r="P3">
-        <v>3.99</v>
+        <v>6.59</v>
       </c>
       <c r="Q3">
-        <v>0.04226694915254237</v>
+        <v>0.05213607594936708</v>
       </c>
       <c r="R3">
-        <v>0.4699646643109541</v>
+        <v>0.4640845070422535</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="V3">
-        <v>0.01747881355932203</v>
+        <v>0.00925632911392405</v>
       </c>
       <c r="W3">
-        <v>0.1604914933837429</v>
+        <v>0.2316476345840131</v>
       </c>
       <c r="X3">
-        <v>0.02814648551717728</v>
+        <v>0.051631436549247</v>
       </c>
       <c r="Y3">
-        <v>0.1323450078665656</v>
+        <v>0.180016198034766</v>
       </c>
       <c r="Z3">
-        <v>0.1059094397544129</v>
+        <v>0.05826017557861134</v>
       </c>
       <c r="AA3">
-        <v>0.06567222493546361</v>
+        <v>0.03172873300963674</v>
       </c>
       <c r="AB3">
-        <v>0.02357614217509286</v>
+        <v>0.04976033340366019</v>
       </c>
       <c r="AC3">
-        <v>0.04209608276037075</v>
+        <v>-0.01803160039402344</v>
       </c>
       <c r="AD3">
-        <v>80.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>80.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="AG3">
-        <v>78.75</v>
+        <v>59.53</v>
       </c>
       <c r="AH3">
-        <v>0.459954233409611</v>
+        <v>0.3244254409406734</v>
       </c>
       <c r="AI3">
-        <v>0.5710227272727273</v>
+        <v>0.5024834437086092</v>
       </c>
       <c r="AJ3">
-        <v>0.4548079699682356</v>
+        <v>0.32017425912978</v>
       </c>
       <c r="AK3">
-        <v>0.5659360402443406</v>
+        <v>0.4976176544345064</v>
       </c>
       <c r="AL3">
-        <v>1.41</v>
+        <v>-3.55</v>
       </c>
       <c r="AM3">
-        <v>1.41</v>
+        <v>-3.55</v>
       </c>
       <c r="AN3">
-        <v>7.17857142857143</v>
+        <v>10.78152753108348</v>
       </c>
       <c r="AO3">
-        <v>7.872340425531915</v>
+        <v>-1.574647887323944</v>
       </c>
       <c r="AP3">
-        <v>7.031250000000001</v>
+        <v>10.57371225577265</v>
       </c>
       <c r="AQ3">
-        <v>7.872340425531915</v>
+        <v>-1.574647887323944</v>
       </c>
     </row>
     <row r="4">
@@ -856,31 +856,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0</v>
+        <v>0.0365</v>
       </c>
       <c r="H4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>-6.31</v>
+        <v>-4.98</v>
       </c>
       <c r="L4">
-        <v>17.24043715846994</v>
+        <v>-0.4980000000000001</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.061</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.001119266055045872</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.01224899598393574</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -892,34 +892,37 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.061</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>6.2</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>0.06206206206206206</v>
+        <v>0.04642201834862385</v>
       </c>
       <c r="W4">
-        <v>-11.07017543859649</v>
+        <v>-0.1676767676767677</v>
       </c>
       <c r="X4">
-        <v>0.02293891894203839</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="Y4">
-        <v>-11.09311435753853</v>
+        <v>-0.2158116218882305</v>
       </c>
       <c r="Z4">
-        <v>-0.6421052631578947</v>
+        <v>3.448275862068967</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02293891894203839</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AC4">
-        <v>-0.02293891894203839</v>
+        <v>-0.04813485421146283</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -931,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-6.2</v>
+        <v>-2.53</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -940,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.06616862326574173</v>
+        <v>-0.0486819318837791</v>
       </c>
       <c r="AK4">
-        <v>-0.2660944206008584</v>
+        <v>-0.07014139173828667</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.111</v>
+        <v>-2.46</v>
       </c>
       <c r="AQ4">
         <v>-0</v>

--- a/research/traditional_assets/database/data/denmark/denmark_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00231</v>
+        <v>0.0246</v>
       </c>
       <c r="E2">
-        <v>0.388</v>
+        <v>0.0562</v>
       </c>
       <c r="G2">
-        <v>0.3325013865779257</v>
+        <v>0.2346460883448643</v>
       </c>
       <c r="H2">
-        <v>0.3122573488630061</v>
+        <v>0.2203299627461416</v>
       </c>
       <c r="I2">
-        <v>0.310038824181919</v>
+        <v>0.1766897285790314</v>
       </c>
       <c r="J2">
-        <v>0.2762942670748261</v>
+        <v>0.1564831904702592</v>
       </c>
       <c r="K2">
-        <v>9.219999999999999</v>
+        <v>-8.75</v>
       </c>
       <c r="L2">
-        <v>0.5113699389905711</v>
+        <v>-0.4656732304417243</v>
       </c>
       <c r="M2">
-        <v>6.651</v>
+        <v>7.091</v>
       </c>
       <c r="N2">
-        <v>0.03676616915422885</v>
+        <v>0.06620915032679739</v>
       </c>
       <c r="O2">
-        <v>0.7213665943600869</v>
+        <v>-0.8104</v>
       </c>
       <c r="P2">
-        <v>6.59</v>
+        <v>7.09</v>
       </c>
       <c r="Q2">
-        <v>0.03642896627971254</v>
+        <v>0.06619981325863679</v>
       </c>
       <c r="R2">
-        <v>0.7147505422993493</v>
+        <v>-0.8102857142857143</v>
       </c>
       <c r="S2">
-        <v>0.061</v>
+        <v>0.001</v>
       </c>
       <c r="T2">
-        <v>0.00917155314990227</v>
+        <v>0.0001410238330277817</v>
       </c>
       <c r="U2">
-        <v>3.7</v>
+        <v>1.438</v>
       </c>
       <c r="V2">
-        <v>0.02045328911000553</v>
+        <v>0.01342670401493931</v>
       </c>
       <c r="W2">
-        <v>0.03198543345362267</v>
+        <v>-0.1896723851052843</v>
       </c>
       <c r="X2">
-        <v>0.04988314538035492</v>
+        <v>0.05476104116113421</v>
       </c>
       <c r="Y2">
-        <v>-0.01789771192673224</v>
+        <v>-0.2444334262664185</v>
       </c>
       <c r="Z2">
-        <v>0.1281176721381369</v>
+        <v>0.1448571472624389</v>
       </c>
       <c r="AA2">
-        <v>0.01586436650481837</v>
+        <v>-0.2683843133840122</v>
       </c>
       <c r="AB2">
-        <v>0.04894759380756151</v>
+        <v>0.05072509125869974</v>
       </c>
       <c r="AC2">
-        <v>-0.03308322730274314</v>
+        <v>-0.3191094046427119</v>
       </c>
       <c r="AD2">
-        <v>60.7</v>
+        <v>76.33</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>60.7</v>
+        <v>76.33</v>
       </c>
       <c r="AG2">
-        <v>57</v>
+        <v>74.892</v>
       </c>
       <c r="AH2">
-        <v>0.2512417218543046</v>
+        <v>0.4161260426320667</v>
       </c>
       <c r="AI2">
-        <v>0.3808030112923463</v>
+        <v>0.4754874478290662</v>
       </c>
       <c r="AJ2">
-        <v>0.2395964691046658</v>
+        <v>0.4115125939601741</v>
       </c>
       <c r="AK2">
-        <v>0.3660886319845857</v>
+        <v>0.4707464863098082</v>
       </c>
       <c r="AL2">
-        <v>-3.55</v>
+        <v>5.15</v>
       </c>
       <c r="AM2">
-        <v>-6.01</v>
+        <v>5.15</v>
       </c>
       <c r="AN2">
-        <v>10.78152753108348</v>
+        <v>16.48596112311015</v>
       </c>
       <c r="AO2">
-        <v>-1.574647887323944</v>
+        <v>0.6446601941747573</v>
       </c>
       <c r="AP2">
-        <v>10.12433392539964</v>
+        <v>16.17537796976242</v>
       </c>
       <c r="AQ2">
-        <v>-0.9301164725457571</v>
+        <v>0.6446601941747573</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00231</v>
+        <v>0.0246</v>
       </c>
       <c r="E3">
-        <v>0.388</v>
+        <v>0.0562</v>
       </c>
       <c r="G3">
-        <v>0.701120797011208</v>
+        <v>0.7882352941176471</v>
       </c>
       <c r="H3">
-        <v>0.701120797011208</v>
+        <v>0.7882352941176471</v>
       </c>
       <c r="I3">
-        <v>0.6961394769613948</v>
+        <v>0.7848739495798319</v>
       </c>
       <c r="J3">
-        <v>0.544604143302395</v>
+        <v>0.605354907920615</v>
       </c>
       <c r="K3">
-        <v>14.2</v>
+        <v>4.35</v>
       </c>
       <c r="L3">
-        <v>1.768368617683686</v>
+        <v>0.3655462184873949</v>
       </c>
       <c r="M3">
-        <v>6.59</v>
+        <v>7.09</v>
       </c>
       <c r="N3">
-        <v>0.05213607594936708</v>
+        <v>0.08390532544378698</v>
       </c>
       <c r="O3">
-        <v>0.4640845070422535</v>
+        <v>1.629885057471264</v>
       </c>
       <c r="P3">
-        <v>6.59</v>
+        <v>7.09</v>
       </c>
       <c r="Q3">
-        <v>0.05213607594936708</v>
+        <v>0.08390532544378698</v>
       </c>
       <c r="R3">
-        <v>0.4640845070422535</v>
+        <v>1.629885057471264</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.17</v>
+        <v>0.068</v>
       </c>
       <c r="V3">
-        <v>0.00925632911392405</v>
+        <v>0.0008047337278106509</v>
       </c>
       <c r="W3">
-        <v>0.2316476345840131</v>
+        <v>0.07237936772046588</v>
       </c>
       <c r="X3">
-        <v>0.051631436549247</v>
+        <v>0.05680371745047592</v>
       </c>
       <c r="Y3">
-        <v>0.180016198034766</v>
+        <v>0.01557565026998996</v>
       </c>
       <c r="Z3">
-        <v>0.05826017557861134</v>
+        <v>0.09947337624341719</v>
       </c>
       <c r="AA3">
-        <v>0.03172873300963674</v>
+        <v>0.0602166965163865</v>
       </c>
       <c r="AB3">
-        <v>0.04976033340366019</v>
+        <v>0.05005255345016459</v>
       </c>
       <c r="AC3">
-        <v>-0.01803160039402344</v>
+        <v>0.01016414306622191</v>
       </c>
       <c r="AD3">
-        <v>60.7</v>
+        <v>68.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>60.7</v>
+        <v>68.7</v>
       </c>
       <c r="AG3">
-        <v>59.53</v>
+        <v>68.63200000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3244254409406734</v>
+        <v>0.4484334203655353</v>
       </c>
       <c r="AI3">
-        <v>0.5024834437086092</v>
+        <v>0.5260336906584993</v>
       </c>
       <c r="AJ3">
-        <v>0.32017425912978</v>
+        <v>0.4481884909751064</v>
       </c>
       <c r="AK3">
-        <v>0.4976176544345064</v>
+        <v>0.525786780253118</v>
       </c>
       <c r="AL3">
-        <v>-3.55</v>
+        <v>3.13</v>
       </c>
       <c r="AM3">
-        <v>-3.55</v>
+        <v>3.13</v>
       </c>
       <c r="AN3">
-        <v>10.78152753108348</v>
+        <v>7.324093816631129</v>
       </c>
       <c r="AO3">
-        <v>-1.574647887323944</v>
+        <v>2.984025559105431</v>
       </c>
       <c r="AP3">
-        <v>10.57371225577265</v>
+        <v>7.316844349680171</v>
       </c>
       <c r="AQ3">
-        <v>-1.574647887323944</v>
+        <v>2.984025559105431</v>
       </c>
     </row>
     <row r="4">
@@ -856,31 +856,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.0365</v>
+        <v>-0.7214804063860668</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>-0.760522496371553</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>-0.8737300435413643</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>-0.8737300435413643</v>
       </c>
       <c r="K4">
-        <v>-4.98</v>
+        <v>-13.1</v>
       </c>
       <c r="L4">
-        <v>-0.4980000000000001</v>
+        <v>-1.901306240928883</v>
       </c>
       <c r="M4">
-        <v>0.061</v>
+        <v>0.001</v>
       </c>
       <c r="N4">
-        <v>0.001119266055045872</v>
+        <v>4.424778761061947e-05</v>
       </c>
       <c r="O4">
-        <v>-0.01224899598393574</v>
+        <v>-7.633587786259542e-05</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -892,70 +892,79 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0.061</v>
+        <v>0.001</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>1.37</v>
       </c>
       <c r="V4">
-        <v>0.04642201834862385</v>
+        <v>0.06061946902654868</v>
       </c>
       <c r="W4">
-        <v>-0.1676767676767677</v>
+        <v>-0.4517241379310345</v>
       </c>
       <c r="X4">
-        <v>0.04813485421146283</v>
+        <v>0.05271836487179251</v>
       </c>
       <c r="Y4">
-        <v>-0.2158116218882305</v>
+        <v>-0.504442502802827</v>
       </c>
       <c r="Z4">
-        <v>3.448275862068967</v>
+        <v>0.6832606108687029</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>-0.5969853232844109</v>
       </c>
       <c r="AB4">
-        <v>0.04813485421146283</v>
+        <v>0.05139762906723488</v>
       </c>
       <c r="AC4">
-        <v>-0.04813485421146283</v>
+        <v>-0.6483829523516458</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>7.63</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>7.63</v>
       </c>
       <c r="AG4">
-        <v>-2.53</v>
+        <v>6.26</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2523982798544492</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.2549281657200134</v>
       </c>
       <c r="AJ4">
-        <v>-0.0486819318837791</v>
+        <v>0.2169092169092169</v>
       </c>
       <c r="AK4">
-        <v>-0.07014139173828667</v>
+        <v>0.219187675070028</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM4">
-        <v>-2.46</v>
+        <v>2.02</v>
+      </c>
+      <c r="AN4">
+        <v>-1.606315789473684</v>
+      </c>
+      <c r="AO4">
+        <v>-2.98019801980198</v>
+      </c>
+      <c r="AP4">
+        <v>-1.317894736842105</v>
       </c>
       <c r="AQ4">
-        <v>-0</v>
+        <v>-2.98019801980198</v>
       </c>
     </row>
   </sheetData>
